--- a/12345678 (1).xlsx
+++ b/12345678 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE3F53-7303-46BE-8A1F-0C2E63DF50ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512D9C9D-A844-4F21-A603-FD91738A09FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>Not Satisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>IT WAS A GOOD DAY</t>
   </si>
 </sst>
 </file>
@@ -1098,29 +1104,55 @@
       <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B9" s="14">
+        <v>495</v>
+      </c>
+      <c r="C9" s="14">
+        <v>35</v>
+      </c>
+      <c r="D9" s="14">
+        <v>130</v>
+      </c>
+      <c r="E9" s="14">
+        <v>44</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>40</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>994</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>446</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
